--- a/매장리스트.xlsx
+++ b/매장리스트.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/1104263/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/1104263/Desktop/유통망 공사정보/construction_app2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC4C083-42AD-0A4A-A8FF-CFBA6ECBCC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C9986C-BF51-4348-AC14-F0AA2CB42FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2380" yWindow="1500" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="1124">
   <si>
     <t>마케팅팀</t>
   </si>
@@ -3380,6 +3380,22 @@
   </si>
   <si>
     <t>경북 봉화군 봉화읍 봉화로 1161-5, 1층 102호</t>
+  </si>
+  <si>
+    <t>D336790053</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상상대리점 청도점</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자가매장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 청도군 청도읍 청화로 139 1층</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3755,7 +3771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L297"/>
+  <dimension ref="A1:L298"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -10117,34 +10133,34 @@
         <v>379</v>
       </c>
       <c r="B188" t="s">
-        <v>706</v>
+        <v>617</v>
       </c>
       <c r="C188" t="s">
-        <v>707</v>
+        <v>618</v>
       </c>
       <c r="D188" t="s">
-        <v>708</v>
+        <v>1120</v>
       </c>
       <c r="E188" t="s">
-        <v>709</v>
+        <v>1121</v>
       </c>
       <c r="F188" t="s">
-        <v>17</v>
+        <v>1122</v>
       </c>
       <c r="H188" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I188" t="s">
         <v>29</v>
       </c>
       <c r="J188">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K188" t="s">
-        <v>710</v>
+        <v>1123</v>
       </c>
       <c r="L188" s="2">
-        <v>42454</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -10158,25 +10174,28 @@
         <v>707</v>
       </c>
       <c r="D189" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E189" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F189" t="s">
         <v>17</v>
+      </c>
+      <c r="H189" t="s">
+        <v>53</v>
       </c>
       <c r="I189" t="s">
         <v>29</v>
       </c>
       <c r="J189">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K189" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="L189" s="2">
-        <v>42474</v>
+        <v>42454</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -10184,31 +10203,31 @@
         <v>379</v>
       </c>
       <c r="B190" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C190" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="D190" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="E190" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="F190" t="s">
         <v>17</v>
       </c>
-      <c r="H190" t="s">
-        <v>18</v>
+      <c r="I190" t="s">
+        <v>29</v>
       </c>
       <c r="J190">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K190" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="L190" s="2">
-        <v>42157</v>
+        <v>42474</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -10216,34 +10235,31 @@
         <v>379</v>
       </c>
       <c r="B191" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C191" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="D191" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="E191" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F191" t="s">
         <v>17</v>
       </c>
       <c r="H191" t="s">
-        <v>53</v>
-      </c>
-      <c r="I191" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J191">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K191" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="L191" s="2">
-        <v>42334</v>
+        <v>42157</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -10257,25 +10273,25 @@
         <v>720</v>
       </c>
       <c r="D192" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E192" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F192" t="s">
         <v>17</v>
       </c>
       <c r="H192" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I192" t="s">
         <v>29</v>
       </c>
       <c r="J192">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K192" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="L192" s="2">
         <v>42334</v>
@@ -10292,28 +10308,28 @@
         <v>720</v>
       </c>
       <c r="D193" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E193" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F193" t="s">
         <v>17</v>
       </c>
       <c r="H193" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="I193" t="s">
         <v>29</v>
       </c>
       <c r="J193">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="K193" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="L193" s="2">
-        <v>42342</v>
+        <v>42334</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -10327,10 +10343,10 @@
         <v>720</v>
       </c>
       <c r="D194" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E194" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F194" t="s">
         <v>17</v>
@@ -10342,13 +10358,13 @@
         <v>29</v>
       </c>
       <c r="J194">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K194" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="L194" s="2">
-        <v>42376</v>
+        <v>42342</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -10362,10 +10378,10 @@
         <v>720</v>
       </c>
       <c r="D195" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E195" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F195" t="s">
         <v>17</v>
@@ -10377,13 +10393,13 @@
         <v>29</v>
       </c>
       <c r="J195">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K195" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="L195" s="2">
-        <v>42422</v>
+        <v>42376</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -10391,22 +10407,22 @@
         <v>379</v>
       </c>
       <c r="B196" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
       <c r="C196" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="D196" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="E196" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="F196" t="s">
         <v>17</v>
       </c>
       <c r="H196" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="I196" t="s">
         <v>29</v>
@@ -10415,10 +10431,10 @@
         <v>20</v>
       </c>
       <c r="K196" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="L196" s="2">
-        <v>42513</v>
+        <v>42422</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -10426,34 +10442,34 @@
         <v>379</v>
       </c>
       <c r="B197" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C197" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D197" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="E197" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="F197" t="s">
         <v>17</v>
       </c>
       <c r="H197" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I197" t="s">
         <v>29</v>
       </c>
       <c r="J197">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K197" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="L197" s="2">
-        <v>43388</v>
+        <v>42513</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -10467,19 +10483,25 @@
         <v>742</v>
       </c>
       <c r="D198" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E198" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F198" t="s">
         <v>17</v>
       </c>
+      <c r="H198" t="s">
+        <v>53</v>
+      </c>
+      <c r="I198" t="s">
+        <v>29</v>
+      </c>
       <c r="J198">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K198" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="L198" s="2">
         <v>43388</v>
@@ -10496,25 +10518,19 @@
         <v>742</v>
       </c>
       <c r="D199" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E199" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="F199" t="s">
         <v>17</v>
       </c>
-      <c r="H199" t="s">
-        <v>53</v>
-      </c>
-      <c r="I199" t="s">
-        <v>29</v>
-      </c>
       <c r="J199">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K199" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="L199" s="2">
         <v>43388</v>
@@ -10531,10 +10547,10 @@
         <v>742</v>
       </c>
       <c r="D200" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E200" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F200" t="s">
         <v>17</v>
@@ -10546,13 +10562,13 @@
         <v>29</v>
       </c>
       <c r="J200">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K200" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="L200" s="2">
-        <v>43409</v>
+        <v>43388</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -10566,10 +10582,10 @@
         <v>742</v>
       </c>
       <c r="D201" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E201" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F201" t="s">
         <v>17</v>
@@ -10581,13 +10597,13 @@
         <v>29</v>
       </c>
       <c r="J201">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K201" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="L201" s="2">
-        <v>43446</v>
+        <v>43409</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -10601,10 +10617,10 @@
         <v>742</v>
       </c>
       <c r="D202" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E202" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="F202" t="s">
         <v>17</v>
@@ -10616,10 +10632,10 @@
         <v>29</v>
       </c>
       <c r="J202">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K202" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="L202" s="2">
         <v>43446</v>
@@ -10636,10 +10652,10 @@
         <v>742</v>
       </c>
       <c r="D203" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E203" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="F203" t="s">
         <v>17</v>
@@ -10648,16 +10664,16 @@
         <v>53</v>
       </c>
       <c r="I203" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="J203">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K203" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="L203" s="2">
-        <v>43572</v>
+        <v>43446</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -10671,10 +10687,10 @@
         <v>742</v>
       </c>
       <c r="D204" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E204" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="F204" t="s">
         <v>17</v>
@@ -10683,16 +10699,16 @@
         <v>53</v>
       </c>
       <c r="I204" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="J204">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K204" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L204" s="2">
-        <v>43859</v>
+        <v>43572</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -10706,31 +10722,28 @@
         <v>742</v>
       </c>
       <c r="D205" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E205" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="F205" t="s">
-        <v>213</v>
-      </c>
-      <c r="G205" t="s">
-        <v>769</v>
+        <v>17</v>
       </c>
       <c r="H205" t="s">
         <v>53</v>
       </c>
       <c r="I205" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="J205">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="K205" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="L205" s="2">
-        <v>44383</v>
+        <v>43859</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -10744,16 +10757,16 @@
         <v>742</v>
       </c>
       <c r="D206" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="E206" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="F206" t="s">
         <v>213</v>
       </c>
       <c r="G206" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="H206" t="s">
         <v>53</v>
@@ -10762,13 +10775,13 @@
         <v>121</v>
       </c>
       <c r="J206">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K206" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="L206" s="2">
-        <v>45127</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -10782,28 +10795,31 @@
         <v>742</v>
       </c>
       <c r="D207" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E207" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="F207" t="s">
-        <v>17</v>
+        <v>213</v>
+      </c>
+      <c r="G207" t="s">
+        <v>773</v>
       </c>
       <c r="H207" t="s">
         <v>53</v>
       </c>
       <c r="I207" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="J207">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="K207" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="L207" s="2">
-        <v>45362</v>
+        <v>45127</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -10817,28 +10833,28 @@
         <v>742</v>
       </c>
       <c r="D208" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E208" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="F208" t="s">
         <v>17</v>
       </c>
       <c r="H208" t="s">
-        <v>780</v>
+        <v>53</v>
       </c>
       <c r="I208" t="s">
         <v>29</v>
       </c>
       <c r="J208">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K208" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="L208" s="2">
-        <v>45665</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -10852,16 +10868,13 @@
         <v>742</v>
       </c>
       <c r="D209" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="E209" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="F209" t="s">
-        <v>213</v>
-      </c>
-      <c r="G209" t="s">
-        <v>255</v>
+        <v>17</v>
       </c>
       <c r="H209" t="s">
         <v>780</v>
@@ -10870,13 +10883,13 @@
         <v>29</v>
       </c>
       <c r="J209">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="K209" t="s">
-        <v>257</v>
+        <v>781</v>
       </c>
       <c r="L209" s="2">
-        <v>45915</v>
+        <v>45665</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -10890,28 +10903,31 @@
         <v>742</v>
       </c>
       <c r="D210" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E210" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F210" t="s">
-        <v>17</v>
+        <v>213</v>
+      </c>
+      <c r="G210" t="s">
+        <v>255</v>
       </c>
       <c r="H210" t="s">
-        <v>18</v>
+        <v>780</v>
       </c>
       <c r="I210" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="J210">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="K210" t="s">
-        <v>786</v>
+        <v>257</v>
       </c>
       <c r="L210" s="2">
-        <v>46013</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -10919,16 +10935,16 @@
         <v>379</v>
       </c>
       <c r="B211" t="s">
-        <v>787</v>
+        <v>741</v>
       </c>
       <c r="C211" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="D211" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="E211" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="F211" t="s">
         <v>17</v>
@@ -10940,13 +10956,13 @@
         <v>152</v>
       </c>
       <c r="J211">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K211" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="L211" s="2">
-        <v>45034</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -10954,16 +10970,16 @@
         <v>379</v>
       </c>
       <c r="B212" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="C212" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="D212" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="E212" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="F212" t="s">
         <v>17</v>
@@ -10975,13 +10991,13 @@
         <v>152</v>
       </c>
       <c r="J212">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K212" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="L212" s="2">
-        <v>45252</v>
+        <v>45034</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -10989,16 +11005,16 @@
         <v>379</v>
       </c>
       <c r="B213" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="C213" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="D213" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="E213" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="F213" t="s">
         <v>17</v>
@@ -11007,16 +11023,16 @@
         <v>18</v>
       </c>
       <c r="I213" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="J213">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K213" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="L213" s="2">
-        <v>45629</v>
+        <v>45252</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -11030,10 +11046,10 @@
         <v>798</v>
       </c>
       <c r="D214" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E214" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F214" t="s">
         <v>17</v>
@@ -11045,30 +11061,30 @@
         <v>29</v>
       </c>
       <c r="J214">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K214" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="L214" s="2">
-        <v>45712</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="215" spans="1:12">
       <c r="A215" t="s">
-        <v>805</v>
+        <v>379</v>
       </c>
       <c r="B215" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="C215" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="D215" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="E215" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="F215" t="s">
         <v>17</v>
@@ -11076,14 +11092,17 @@
       <c r="H215" t="s">
         <v>18</v>
       </c>
+      <c r="I215" t="s">
+        <v>29</v>
+      </c>
       <c r="J215">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K215" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="L215" s="2">
-        <v>33950</v>
+        <v>45712</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -11091,16 +11110,16 @@
         <v>805</v>
       </c>
       <c r="B216" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C216" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="D216" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="E216" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="F216" t="s">
         <v>17</v>
@@ -11109,10 +11128,10 @@
         <v>18</v>
       </c>
       <c r="J216">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K216" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="L216" s="2">
         <v>33950</v>
@@ -11123,16 +11142,16 @@
         <v>805</v>
       </c>
       <c r="B217" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="C217" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="D217" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="E217" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="F217" t="s">
         <v>17</v>
@@ -11144,10 +11163,10 @@
         <v>25</v>
       </c>
       <c r="K217" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="L217" s="2">
-        <v>34620</v>
+        <v>33950</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -11155,16 +11174,16 @@
         <v>805</v>
       </c>
       <c r="B218" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="C218" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="D218" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="E218" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="F218" t="s">
         <v>17</v>
@@ -11173,13 +11192,13 @@
         <v>18</v>
       </c>
       <c r="J218">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K218" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="L218" s="2">
-        <v>34932</v>
+        <v>34620</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -11193,10 +11212,10 @@
         <v>822</v>
       </c>
       <c r="D219" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E219" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="F219" t="s">
         <v>17</v>
@@ -11204,17 +11223,14 @@
       <c r="H219" t="s">
         <v>18</v>
       </c>
-      <c r="I219" t="s">
-        <v>121</v>
-      </c>
       <c r="J219">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="K219" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="L219" s="2">
-        <v>43119</v>
+        <v>34932</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -11228,10 +11244,10 @@
         <v>822</v>
       </c>
       <c r="D220" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E220" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="F220" t="s">
         <v>17</v>
@@ -11240,16 +11256,16 @@
         <v>18</v>
       </c>
       <c r="I220" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="J220">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K220" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="L220" s="2">
-        <v>44375</v>
+        <v>43119</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -11257,16 +11273,16 @@
         <v>805</v>
       </c>
       <c r="B221" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="C221" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="D221" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="E221" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="F221" t="s">
         <v>17</v>
@@ -11274,14 +11290,17 @@
       <c r="H221" t="s">
         <v>18</v>
       </c>
+      <c r="I221" t="s">
+        <v>152</v>
+      </c>
       <c r="J221">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K221" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="L221" s="2">
-        <v>35217</v>
+        <v>44375</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -11289,16 +11308,16 @@
         <v>805</v>
       </c>
       <c r="B222" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C222" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="D222" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="E222" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="F222" t="s">
         <v>17</v>
@@ -11306,17 +11325,14 @@
       <c r="H222" t="s">
         <v>18</v>
       </c>
-      <c r="I222" t="s">
-        <v>29</v>
-      </c>
       <c r="J222">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="L222" s="2">
-        <v>41123</v>
+        <v>35217</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -11330,10 +11346,10 @@
         <v>838</v>
       </c>
       <c r="D223" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E223" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="F223" t="s">
         <v>17</v>
@@ -11342,16 +11358,16 @@
         <v>18</v>
       </c>
       <c r="I223" t="s">
-        <v>256</v>
+        <v>29</v>
       </c>
       <c r="J223">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="K223" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="L223" s="2">
-        <v>41774</v>
+        <v>41123</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -11365,28 +11381,28 @@
         <v>838</v>
       </c>
       <c r="D224" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E224" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="F224" t="s">
         <v>17</v>
       </c>
       <c r="H224" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I224" t="s">
-        <v>29</v>
+        <v>256</v>
       </c>
       <c r="J224">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="K224" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="L224" s="2">
-        <v>42760</v>
+        <v>41774</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -11400,28 +11416,28 @@
         <v>838</v>
       </c>
       <c r="D225" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E225" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="F225" t="s">
         <v>17</v>
       </c>
       <c r="H225" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I225" t="s">
         <v>29</v>
       </c>
       <c r="J225">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K225" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="L225" s="2">
-        <v>42919</v>
+        <v>42760</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -11435,10 +11451,10 @@
         <v>838</v>
       </c>
       <c r="D226" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E226" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F226" t="s">
         <v>17</v>
@@ -11447,16 +11463,16 @@
         <v>18</v>
       </c>
       <c r="I226" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="J226">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K226" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="L226" s="2">
-        <v>43074</v>
+        <v>42919</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -11470,10 +11486,10 @@
         <v>838</v>
       </c>
       <c r="D227" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E227" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="F227" t="s">
         <v>17</v>
@@ -11482,16 +11498,16 @@
         <v>18</v>
       </c>
       <c r="I227" t="s">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="J227">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="K227" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="L227" s="2">
-        <v>44048</v>
+        <v>43074</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -11505,10 +11521,10 @@
         <v>838</v>
       </c>
       <c r="D228" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="E228" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="F228" t="s">
         <v>17</v>
@@ -11520,13 +11536,13 @@
         <v>152</v>
       </c>
       <c r="J228">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="K228" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="L228" s="2">
-        <v>44218</v>
+        <v>44048</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -11540,10 +11556,10 @@
         <v>838</v>
       </c>
       <c r="D229" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E229" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="F229" t="s">
         <v>17</v>
@@ -11552,16 +11568,16 @@
         <v>18</v>
       </c>
       <c r="I229" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="J229">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K229" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="L229" s="2">
-        <v>44396</v>
+        <v>44218</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -11575,31 +11591,28 @@
         <v>838</v>
       </c>
       <c r="D230" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="E230" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="F230" t="s">
-        <v>213</v>
-      </c>
-      <c r="G230" t="s">
-        <v>865</v>
+        <v>17</v>
       </c>
       <c r="H230" t="s">
         <v>18</v>
       </c>
       <c r="I230" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="J230">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K230" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="L230" s="2">
-        <v>45342</v>
+        <v>44396</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -11613,28 +11626,31 @@
         <v>838</v>
       </c>
       <c r="D231" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="E231" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="F231" t="s">
-        <v>17</v>
+        <v>213</v>
+      </c>
+      <c r="G231" t="s">
+        <v>865</v>
       </c>
       <c r="H231" t="s">
         <v>18</v>
       </c>
       <c r="I231" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="J231">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K231" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="L231" s="2">
-        <v>45897</v>
+        <v>45342</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -11642,16 +11658,16 @@
         <v>805</v>
       </c>
       <c r="B232" t="s">
-        <v>870</v>
+        <v>837</v>
       </c>
       <c r="C232" t="s">
-        <v>871</v>
+        <v>838</v>
       </c>
       <c r="D232" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E232" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="F232" t="s">
         <v>17</v>
@@ -11659,14 +11675,17 @@
       <c r="H232" t="s">
         <v>18</v>
       </c>
+      <c r="I232" t="s">
+        <v>29</v>
+      </c>
       <c r="J232">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="K232" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="L232" s="2">
-        <v>39366</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -11680,10 +11699,10 @@
         <v>871</v>
       </c>
       <c r="D233" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="E233" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F233" t="s">
         <v>17</v>
@@ -11691,17 +11710,14 @@
       <c r="H233" t="s">
         <v>18</v>
       </c>
-      <c r="I233" t="s">
-        <v>29</v>
-      </c>
       <c r="J233">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K233" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="L233" s="2">
-        <v>41137</v>
+        <v>39366</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -11709,16 +11725,16 @@
         <v>805</v>
       </c>
       <c r="B234" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="C234" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="D234" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E234" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="F234" t="s">
         <v>17</v>
@@ -11726,14 +11742,17 @@
       <c r="H234" t="s">
         <v>18</v>
       </c>
+      <c r="I234" t="s">
+        <v>29</v>
+      </c>
       <c r="J234">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K234" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="L234" s="2">
-        <v>40716</v>
+        <v>41137</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -11741,16 +11760,16 @@
         <v>805</v>
       </c>
       <c r="B235" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C235" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="D235" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E235" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F235" t="s">
         <v>17</v>
@@ -11758,17 +11777,14 @@
       <c r="H235" t="s">
         <v>18</v>
       </c>
-      <c r="I235" t="s">
-        <v>29</v>
-      </c>
       <c r="J235">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="K235" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="L235" s="2">
-        <v>41606</v>
+        <v>40716</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -11776,16 +11792,16 @@
         <v>805</v>
       </c>
       <c r="B236" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C236" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="D236" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="E236" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="F236" t="s">
         <v>17</v>
@@ -11793,14 +11809,17 @@
       <c r="H236" t="s">
         <v>18</v>
       </c>
+      <c r="I236" t="s">
+        <v>29</v>
+      </c>
       <c r="J236">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K236" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="L236" s="2">
-        <v>35554</v>
+        <v>41606</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -11814,10 +11833,10 @@
         <v>889</v>
       </c>
       <c r="D237" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="E237" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="F237" t="s">
         <v>17</v>
@@ -11826,13 +11845,13 @@
         <v>18</v>
       </c>
       <c r="J237">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K237" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="L237" s="2">
-        <v>38029</v>
+        <v>35554</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -11846,10 +11865,10 @@
         <v>889</v>
       </c>
       <c r="D238" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="E238" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="F238" t="s">
         <v>17</v>
@@ -11858,13 +11877,13 @@
         <v>18</v>
       </c>
       <c r="J238">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K238" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="L238" s="2">
-        <v>40169</v>
+        <v>38029</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -11878,10 +11897,10 @@
         <v>889</v>
       </c>
       <c r="D239" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="E239" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="F239" t="s">
         <v>17</v>
@@ -11890,13 +11909,13 @@
         <v>18</v>
       </c>
       <c r="J239">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K239" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="L239" s="2">
-        <v>40708</v>
+        <v>40169</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -11910,10 +11929,10 @@
         <v>889</v>
       </c>
       <c r="D240" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="E240" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="F240" t="s">
         <v>17</v>
@@ -11921,17 +11940,14 @@
       <c r="H240" t="s">
         <v>18</v>
       </c>
-      <c r="I240" t="s">
-        <v>29</v>
-      </c>
       <c r="J240">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K240" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="L240" s="2">
-        <v>43948</v>
+        <v>40708</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -11945,10 +11961,10 @@
         <v>889</v>
       </c>
       <c r="D241" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="E241" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="F241" t="s">
         <v>17</v>
@@ -11960,13 +11976,13 @@
         <v>29</v>
       </c>
       <c r="J241">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K241" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="L241" s="2">
-        <v>43955</v>
+        <v>43948</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -11980,16 +11996,16 @@
         <v>889</v>
       </c>
       <c r="D242" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="E242" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F242" t="s">
         <v>17</v>
       </c>
       <c r="H242" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I242" t="s">
         <v>29</v>
@@ -11998,10 +12014,10 @@
         <v>15</v>
       </c>
       <c r="K242" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="L242" s="2">
-        <v>45679</v>
+        <v>43955</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -12009,31 +12025,34 @@
         <v>805</v>
       </c>
       <c r="B243" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="C243" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
       <c r="D243" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="E243" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="F243" t="s">
         <v>17</v>
       </c>
       <c r="H243" t="s">
-        <v>18</v>
+        <v>53</v>
+      </c>
+      <c r="I243" t="s">
+        <v>29</v>
       </c>
       <c r="J243">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K243" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="L243" s="2">
-        <v>35557</v>
+        <v>45679</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -12041,16 +12060,16 @@
         <v>805</v>
       </c>
       <c r="B244" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="C244" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="D244" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="E244" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="F244" t="s">
         <v>17</v>
@@ -12058,17 +12077,14 @@
       <c r="H244" t="s">
         <v>18</v>
       </c>
-      <c r="I244" t="s">
-        <v>29</v>
-      </c>
       <c r="J244">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K244" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="L244" s="2">
-        <v>41228</v>
+        <v>35557</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -12076,16 +12092,16 @@
         <v>805</v>
       </c>
       <c r="B245" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C245" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="D245" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="E245" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="F245" t="s">
         <v>17</v>
@@ -12093,14 +12109,17 @@
       <c r="H245" t="s">
         <v>18</v>
       </c>
+      <c r="I245" t="s">
+        <v>29</v>
+      </c>
       <c r="J245">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K245" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="L245" s="2">
-        <v>37907</v>
+        <v>41228</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -12108,16 +12127,16 @@
         <v>805</v>
       </c>
       <c r="B246" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C246" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="D246" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="E246" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="F246" t="s">
         <v>17</v>
@@ -12126,13 +12145,13 @@
         <v>18</v>
       </c>
       <c r="J246">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K246" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="L246" s="2">
-        <v>38834</v>
+        <v>37907</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -12140,25 +12159,31 @@
         <v>805</v>
       </c>
       <c r="B247" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="C247" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D247" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="E247" t="s">
-        <v>934</v>
+        <v>929</v>
+      </c>
+      <c r="F247" t="s">
+        <v>17</v>
+      </c>
+      <c r="H247" t="s">
+        <v>18</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K247" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="L247" s="2">
-        <v>39812</v>
+        <v>38834</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -12172,25 +12197,19 @@
         <v>932</v>
       </c>
       <c r="D248" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E248" t="s">
-        <v>937</v>
-      </c>
-      <c r="F248" t="s">
-        <v>17</v>
-      </c>
-      <c r="H248" t="s">
-        <v>53</v>
+        <v>934</v>
       </c>
       <c r="J248">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="L248" s="2">
-        <v>39877</v>
+        <v>39812</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -12204,10 +12223,10 @@
         <v>932</v>
       </c>
       <c r="D249" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="E249" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="F249" t="s">
         <v>17</v>
@@ -12216,13 +12235,13 @@
         <v>53</v>
       </c>
       <c r="J249">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="K249" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="L249" s="2">
-        <v>40091</v>
+        <v>39877</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -12236,22 +12255,25 @@
         <v>932</v>
       </c>
       <c r="D250" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="E250" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="F250" t="s">
         <v>17</v>
       </c>
+      <c r="H250" t="s">
+        <v>53</v>
+      </c>
       <c r="J250">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="K250" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="L250" s="2">
-        <v>40098</v>
+        <v>40091</v>
       </c>
     </row>
     <row r="251" spans="1:12">
@@ -12265,25 +12287,22 @@
         <v>932</v>
       </c>
       <c r="D251" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="E251" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="F251" t="s">
         <v>17</v>
       </c>
-      <c r="H251" t="s">
-        <v>179</v>
-      </c>
       <c r="J251">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K251" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="L251" s="2">
-        <v>40353</v>
+        <v>40098</v>
       </c>
     </row>
     <row r="252" spans="1:12">
@@ -12297,28 +12316,25 @@
         <v>932</v>
       </c>
       <c r="D252" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="E252" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="F252" t="s">
         <v>17</v>
       </c>
       <c r="H252" t="s">
-        <v>53</v>
-      </c>
-      <c r="I252" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="J252">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K252" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="L252" s="2">
-        <v>41087</v>
+        <v>40353</v>
       </c>
     </row>
     <row r="253" spans="1:12">
@@ -12332,28 +12348,28 @@
         <v>932</v>
       </c>
       <c r="D253" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E253" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="F253" t="s">
         <v>17</v>
       </c>
       <c r="H253" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="I253" t="s">
         <v>29</v>
       </c>
       <c r="J253">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K253" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="L253" s="2">
-        <v>41520</v>
+        <v>41087</v>
       </c>
     </row>
     <row r="254" spans="1:12">
@@ -12367,28 +12383,28 @@
         <v>932</v>
       </c>
       <c r="D254" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="E254" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="F254" t="s">
         <v>17</v>
       </c>
       <c r="H254" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="I254" t="s">
         <v>29</v>
       </c>
       <c r="J254">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K254" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="L254" s="2">
-        <v>42782</v>
+        <v>41520</v>
       </c>
     </row>
     <row r="255" spans="1:12">
@@ -12402,10 +12418,10 @@
         <v>932</v>
       </c>
       <c r="D255" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="E255" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="F255" t="s">
         <v>17</v>
@@ -12414,16 +12430,16 @@
         <v>53</v>
       </c>
       <c r="I255" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="J255">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K255" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="L255" s="2">
-        <v>43621</v>
+        <v>42782</v>
       </c>
     </row>
     <row r="256" spans="1:12">
@@ -12437,10 +12453,10 @@
         <v>932</v>
       </c>
       <c r="D256" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="E256" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F256" t="s">
         <v>17</v>
@@ -12452,13 +12468,13 @@
         <v>121</v>
       </c>
       <c r="J256">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K256" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="L256" s="2">
-        <v>43670</v>
+        <v>43621</v>
       </c>
     </row>
     <row r="257" spans="1:12">
@@ -12472,10 +12488,10 @@
         <v>932</v>
       </c>
       <c r="D257" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="E257" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F257" t="s">
         <v>17</v>
@@ -12484,16 +12500,16 @@
         <v>53</v>
       </c>
       <c r="I257" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="J257">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="K257" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="L257" s="2">
-        <v>43979</v>
+        <v>43670</v>
       </c>
     </row>
     <row r="258" spans="1:12">
@@ -12507,10 +12523,10 @@
         <v>932</v>
       </c>
       <c r="D258" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="E258" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F258" t="s">
         <v>17</v>
@@ -12522,13 +12538,13 @@
         <v>152</v>
       </c>
       <c r="J258">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K258" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="L258" s="2">
-        <v>44004</v>
+        <v>43979</v>
       </c>
     </row>
     <row r="259" spans="1:12">
@@ -12536,16 +12552,16 @@
         <v>805</v>
       </c>
       <c r="B259" t="s">
-        <v>969</v>
+        <v>931</v>
       </c>
       <c r="C259" t="s">
-        <v>970</v>
+        <v>932</v>
       </c>
       <c r="D259" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="E259" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="F259" t="s">
         <v>17</v>
@@ -12553,14 +12569,17 @@
       <c r="H259" t="s">
         <v>53</v>
       </c>
+      <c r="I259" t="s">
+        <v>152</v>
+      </c>
       <c r="J259">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K259" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="L259" s="2">
-        <v>39848</v>
+        <v>44004</v>
       </c>
     </row>
     <row r="260" spans="1:12">
@@ -12574,25 +12593,25 @@
         <v>970</v>
       </c>
       <c r="D260" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="E260" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="F260" t="s">
         <v>17</v>
       </c>
-      <c r="I260" t="s">
-        <v>74</v>
+      <c r="H260" t="s">
+        <v>53</v>
       </c>
       <c r="J260">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K260" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="L260" s="2">
-        <v>42174</v>
+        <v>39848</v>
       </c>
     </row>
     <row r="261" spans="1:12">
@@ -12606,28 +12625,25 @@
         <v>970</v>
       </c>
       <c r="D261" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E261" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="F261" t="s">
         <v>17</v>
       </c>
-      <c r="H261" t="s">
-        <v>53</v>
-      </c>
       <c r="I261" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="J261">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="K261" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="L261" s="2">
-        <v>43200</v>
+        <v>42174</v>
       </c>
     </row>
     <row r="262" spans="1:12">
@@ -12641,28 +12657,28 @@
         <v>970</v>
       </c>
       <c r="D262" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="E262" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="F262" t="s">
         <v>17</v>
       </c>
       <c r="H262" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I262" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="J262">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K262" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="L262" s="2">
-        <v>43819</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="263" spans="1:12">
@@ -12670,16 +12686,16 @@
         <v>805</v>
       </c>
       <c r="B263" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="C263" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
       <c r="D263" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E263" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="F263" t="s">
         <v>17</v>
@@ -12691,13 +12707,13 @@
         <v>29</v>
       </c>
       <c r="J263">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="K263" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="L263" s="2">
-        <v>41298</v>
+        <v>43819</v>
       </c>
     </row>
     <row r="264" spans="1:12">
@@ -12705,16 +12721,16 @@
         <v>805</v>
       </c>
       <c r="B264" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="C264" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="D264" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="E264" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="F264" t="s">
         <v>17</v>
@@ -12722,14 +12738,17 @@
       <c r="H264" t="s">
         <v>18</v>
       </c>
+      <c r="I264" t="s">
+        <v>29</v>
+      </c>
       <c r="J264">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K264" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="L264" s="2">
-        <v>40141</v>
+        <v>41298</v>
       </c>
     </row>
     <row r="265" spans="1:12">
@@ -12737,16 +12756,16 @@
         <v>805</v>
       </c>
       <c r="B265" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="C265" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="D265" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E265" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F265" t="s">
         <v>17</v>
@@ -12755,13 +12774,13 @@
         <v>18</v>
       </c>
       <c r="J265">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K265" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="L265" s="2">
-        <v>40750</v>
+        <v>40141</v>
       </c>
     </row>
     <row r="266" spans="1:12">
@@ -12769,28 +12788,31 @@
         <v>805</v>
       </c>
       <c r="B266" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="C266" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="D266" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E266" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="F266" t="s">
         <v>17</v>
       </c>
+      <c r="H266" t="s">
+        <v>18</v>
+      </c>
       <c r="J266">
-        <v>105</v>
+        <v>12</v>
       </c>
       <c r="K266" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="L266" s="2">
-        <v>41102</v>
+        <v>40750</v>
       </c>
     </row>
     <row r="267" spans="1:12">
@@ -12804,28 +12826,22 @@
         <v>999</v>
       </c>
       <c r="D267" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="E267" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="F267" t="s">
         <v>17</v>
       </c>
-      <c r="H267" t="s">
-        <v>53</v>
-      </c>
-      <c r="I267" t="s">
-        <v>29</v>
-      </c>
       <c r="J267">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="K267" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="L267" s="2">
-        <v>41318</v>
+        <v>41102</v>
       </c>
     </row>
     <row r="268" spans="1:12">
@@ -12839,28 +12855,28 @@
         <v>999</v>
       </c>
       <c r="D268" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="E268" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="F268" t="s">
         <v>17</v>
       </c>
       <c r="H268" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I268" t="s">
         <v>29</v>
       </c>
       <c r="J268">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K268" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="L268" s="2">
-        <v>42684</v>
+        <v>41318</v>
       </c>
     </row>
     <row r="269" spans="1:12">
@@ -12874,28 +12890,28 @@
         <v>999</v>
       </c>
       <c r="D269" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E269" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="F269" t="s">
         <v>17</v>
       </c>
       <c r="H269" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I269" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="J269">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K269" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="L269" s="2">
-        <v>43684</v>
+        <v>42684</v>
       </c>
     </row>
     <row r="270" spans="1:12">
@@ -12909,10 +12925,10 @@
         <v>999</v>
       </c>
       <c r="D270" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="E270" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="F270" t="s">
         <v>17</v>
@@ -12927,10 +12943,10 @@
         <v>20</v>
       </c>
       <c r="K270" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="L270" s="2">
-        <v>43707</v>
+        <v>43684</v>
       </c>
     </row>
     <row r="271" spans="1:12">
@@ -12944,28 +12960,28 @@
         <v>999</v>
       </c>
       <c r="D271" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E271" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F271" t="s">
         <v>17</v>
       </c>
       <c r="H271" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I271" t="s">
         <v>121</v>
       </c>
       <c r="J271">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K271" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="L271" s="2">
-        <v>43726</v>
+        <v>43707</v>
       </c>
     </row>
     <row r="272" spans="1:12">
@@ -12979,28 +12995,28 @@
         <v>999</v>
       </c>
       <c r="D272" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="E272" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="F272" t="s">
         <v>17</v>
       </c>
       <c r="H272" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I272" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="J272">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K272" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="L272" s="2">
-        <v>43900</v>
+        <v>43726</v>
       </c>
     </row>
     <row r="273" spans="1:12">
@@ -13014,28 +13030,28 @@
         <v>999</v>
       </c>
       <c r="D273" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="E273" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="F273" t="s">
         <v>17</v>
       </c>
       <c r="H273" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I273" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="J273">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K273" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="L273" s="2">
-        <v>44539</v>
+        <v>43900</v>
       </c>
     </row>
     <row r="274" spans="1:12">
@@ -13049,10 +13065,10 @@
         <v>999</v>
       </c>
       <c r="D274" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E274" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="F274" t="s">
         <v>17</v>
@@ -13061,16 +13077,16 @@
         <v>18</v>
       </c>
       <c r="I274" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J274">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="K274" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="L274" s="2">
-        <v>44909</v>
+        <v>44539</v>
       </c>
     </row>
     <row r="275" spans="1:12">
@@ -13084,28 +13100,28 @@
         <v>999</v>
       </c>
       <c r="D275" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E275" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="F275" t="s">
         <v>17</v>
       </c>
       <c r="H275" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I275" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="J275">
         <v>18</v>
       </c>
       <c r="K275" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="L275" s="2">
-        <v>45041</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="276" spans="1:12">
@@ -13119,31 +13135,28 @@
         <v>999</v>
       </c>
       <c r="D276" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="E276" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="F276" t="s">
-        <v>213</v>
-      </c>
-      <c r="G276" t="s">
-        <v>1032</v>
+        <v>17</v>
       </c>
       <c r="H276" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I276" t="s">
         <v>29</v>
       </c>
       <c r="J276">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K276" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="L276" s="2">
-        <v>45043</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="277" spans="1:12">
@@ -13157,28 +13170,31 @@
         <v>999</v>
       </c>
       <c r="D277" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="E277" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="F277" t="s">
-        <v>17</v>
+        <v>213</v>
+      </c>
+      <c r="G277" t="s">
+        <v>1032</v>
       </c>
       <c r="H277" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I277" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="J277">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K277" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="L277" s="2">
-        <v>45216</v>
+        <v>45043</v>
       </c>
     </row>
     <row r="278" spans="1:12">
@@ -13192,31 +13208,28 @@
         <v>999</v>
       </c>
       <c r="D278" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="E278" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="F278" t="s">
-        <v>213</v>
-      </c>
-      <c r="G278" t="s">
-        <v>1039</v>
+        <v>17</v>
       </c>
       <c r="H278" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I278" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="J278">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="K278" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="L278" s="2">
-        <v>45463</v>
+        <v>45216</v>
       </c>
     </row>
     <row r="279" spans="1:12">
@@ -13230,31 +13243,31 @@
         <v>999</v>
       </c>
       <c r="D279" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="E279" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="F279" t="s">
         <v>213</v>
       </c>
       <c r="G279" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="H279" t="s">
         <v>18</v>
       </c>
       <c r="I279" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="J279">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K279" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="L279" s="2">
-        <v>45881</v>
+        <v>45463</v>
       </c>
     </row>
     <row r="280" spans="1:12">
@@ -13262,31 +13275,37 @@
         <v>805</v>
       </c>
       <c r="B280" t="s">
-        <v>1045</v>
+        <v>998</v>
       </c>
       <c r="C280" t="s">
-        <v>1046</v>
+        <v>999</v>
       </c>
       <c r="D280" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="E280" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="F280" t="s">
-        <v>17</v>
+        <v>213</v>
+      </c>
+      <c r="G280" t="s">
+        <v>1043</v>
       </c>
       <c r="H280" t="s">
         <v>18</v>
       </c>
+      <c r="I280" t="s">
+        <v>152</v>
+      </c>
       <c r="J280">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K280" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="L280" s="2">
-        <v>41115</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="281" spans="1:12">
@@ -13294,16 +13313,16 @@
         <v>805</v>
       </c>
       <c r="B281" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C281" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D281" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="E281" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="F281" t="s">
         <v>17</v>
@@ -13312,13 +13331,13 @@
         <v>18</v>
       </c>
       <c r="J281">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K281" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="L281" s="2">
-        <v>41331</v>
+        <v>41115</v>
       </c>
     </row>
     <row r="282" spans="1:12">
@@ -13332,10 +13351,10 @@
         <v>1051</v>
       </c>
       <c r="D282" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E282" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F282" t="s">
         <v>17</v>
@@ -13343,17 +13362,14 @@
       <c r="H282" t="s">
         <v>18</v>
       </c>
-      <c r="I282" t="s">
-        <v>121</v>
-      </c>
       <c r="J282">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K282" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="L282" s="2">
-        <v>42601</v>
+        <v>41331</v>
       </c>
     </row>
     <row r="283" spans="1:12">
@@ -13361,16 +13377,16 @@
         <v>805</v>
       </c>
       <c r="B283" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
       <c r="C283" t="s">
-        <v>1059</v>
+        <v>1051</v>
       </c>
       <c r="D283" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="E283" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="F283" t="s">
         <v>17</v>
@@ -13378,14 +13394,17 @@
       <c r="H283" t="s">
         <v>18</v>
       </c>
+      <c r="I283" t="s">
+        <v>121</v>
+      </c>
       <c r="J283">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K283" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="L283" s="2">
-        <v>41572</v>
+        <v>42601</v>
       </c>
     </row>
     <row r="284" spans="1:12">
@@ -13393,16 +13412,16 @@
         <v>805</v>
       </c>
       <c r="B284" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="C284" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="D284" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="E284" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="F284" t="s">
         <v>17</v>
@@ -13411,13 +13430,13 @@
         <v>18</v>
       </c>
       <c r="J284">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K284" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="L284" s="2">
-        <v>41687</v>
+        <v>41572</v>
       </c>
     </row>
     <row r="285" spans="1:12">
@@ -13425,16 +13444,16 @@
         <v>805</v>
       </c>
       <c r="B285" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="C285" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="D285" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="E285" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="F285" t="s">
         <v>17</v>
@@ -13443,13 +13462,13 @@
         <v>18</v>
       </c>
       <c r="J285">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K285" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="L285" s="2">
-        <v>42093</v>
+        <v>41687</v>
       </c>
     </row>
     <row r="286" spans="1:12">
@@ -13457,16 +13476,16 @@
         <v>805</v>
       </c>
       <c r="B286" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="C286" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="D286" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="E286" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="F286" t="s">
         <v>17</v>
@@ -13475,13 +13494,13 @@
         <v>18</v>
       </c>
       <c r="J286">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K286" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="L286" s="2">
-        <v>42699</v>
+        <v>42093</v>
       </c>
     </row>
     <row r="287" spans="1:12">
@@ -13489,16 +13508,16 @@
         <v>805</v>
       </c>
       <c r="B287" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="C287" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D287" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="E287" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="F287" t="s">
         <v>17</v>
@@ -13506,17 +13525,14 @@
       <c r="H287" t="s">
         <v>18</v>
       </c>
-      <c r="I287" t="s">
-        <v>121</v>
-      </c>
       <c r="J287">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K287" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="L287" s="2">
-        <v>43270</v>
+        <v>42699</v>
       </c>
     </row>
     <row r="288" spans="1:12">
@@ -13530,10 +13546,10 @@
         <v>1079</v>
       </c>
       <c r="D288" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="E288" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="F288" t="s">
         <v>17</v>
@@ -13545,13 +13561,13 @@
         <v>121</v>
       </c>
       <c r="J288">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K288" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="L288" s="2">
-        <v>43637</v>
+        <v>43270</v>
       </c>
     </row>
     <row r="289" spans="1:12">
@@ -13559,16 +13575,16 @@
         <v>805</v>
       </c>
       <c r="B289" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="C289" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="D289" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="E289" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="F289" t="s">
         <v>17</v>
@@ -13577,16 +13593,16 @@
         <v>18</v>
       </c>
       <c r="I289" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="J289">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K289" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="L289" s="2">
-        <v>44194</v>
+        <v>43637</v>
       </c>
     </row>
     <row r="290" spans="1:12">
@@ -13600,28 +13616,28 @@
         <v>1087</v>
       </c>
       <c r="D290" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="E290" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="F290" t="s">
         <v>17</v>
       </c>
       <c r="H290" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I290" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="J290">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K290" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="L290" s="2">
-        <v>45068</v>
+        <v>44194</v>
       </c>
     </row>
     <row r="291" spans="1:12">
@@ -13629,34 +13645,34 @@
         <v>805</v>
       </c>
       <c r="B291" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="C291" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="D291" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="E291" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="F291" t="s">
         <v>17</v>
       </c>
       <c r="H291" t="s">
-        <v>780</v>
+        <v>53</v>
       </c>
       <c r="I291" t="s">
         <v>29</v>
       </c>
       <c r="J291">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K291" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="L291" s="2">
-        <v>45629</v>
+        <v>45068</v>
       </c>
     </row>
     <row r="292" spans="1:12">
@@ -13670,25 +13686,25 @@
         <v>1095</v>
       </c>
       <c r="D292" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="E292" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="F292" t="s">
         <v>17</v>
       </c>
       <c r="H292" t="s">
-        <v>18</v>
+        <v>780</v>
       </c>
       <c r="I292" t="s">
         <v>29</v>
       </c>
       <c r="J292">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K292" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="L292" s="2">
         <v>45629</v>
@@ -13705,10 +13721,10 @@
         <v>1095</v>
       </c>
       <c r="D293" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E293" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="F293" t="s">
         <v>17</v>
@@ -13720,13 +13736,13 @@
         <v>29</v>
       </c>
       <c r="J293">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K293" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="L293" s="2">
-        <v>45643</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="294" spans="1:12">
@@ -13740,28 +13756,28 @@
         <v>1095</v>
       </c>
       <c r="D294" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="E294" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="F294" t="s">
         <v>17</v>
       </c>
       <c r="H294" t="s">
-        <v>780</v>
+        <v>18</v>
       </c>
       <c r="I294" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="J294">
         <v>20</v>
       </c>
       <c r="K294" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="L294" s="2">
-        <v>45646</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="295" spans="1:12">
@@ -13775,31 +13791,28 @@
         <v>1095</v>
       </c>
       <c r="D295" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="E295" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="F295" t="s">
-        <v>213</v>
-      </c>
-      <c r="G295" t="s">
-        <v>1110</v>
+        <v>17</v>
       </c>
       <c r="H295" t="s">
-        <v>179</v>
+        <v>780</v>
       </c>
       <c r="I295" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="J295">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K295" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="L295" s="2">
-        <v>45664</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="296" spans="1:12">
@@ -13813,28 +13826,31 @@
         <v>1095</v>
       </c>
       <c r="D296" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="E296" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="F296" t="s">
-        <v>17</v>
+        <v>213</v>
+      </c>
+      <c r="G296" t="s">
+        <v>1110</v>
       </c>
       <c r="H296" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="I296" t="s">
         <v>29</v>
       </c>
       <c r="J296">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K296" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="L296" s="2">
-        <v>46013</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="297" spans="1:12">
@@ -13842,16 +13858,16 @@
         <v>805</v>
       </c>
       <c r="B297" t="s">
-        <v>1115</v>
+        <v>1094</v>
       </c>
       <c r="C297" t="s">
-        <v>1116</v>
+        <v>1095</v>
       </c>
       <c r="D297" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="E297" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="F297" t="s">
         <v>17</v>
@@ -13863,12 +13879,47 @@
         <v>29</v>
       </c>
       <c r="J297">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K297" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L297" s="2">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12">
+      <c r="A298" t="s">
+        <v>805</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E298" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F298" t="s">
+        <v>17</v>
+      </c>
+      <c r="H298" t="s">
+        <v>18</v>
+      </c>
+      <c r="I298" t="s">
+        <v>29</v>
+      </c>
+      <c r="J298">
+        <v>17</v>
+      </c>
+      <c r="K298" t="s">
         <v>1119</v>
       </c>
-      <c r="L297" s="2">
+      <c r="L298" s="2">
         <v>45764</v>
       </c>
     </row>
